--- a/model/机械臂部件重量清单.xlsx
+++ b/model/机械臂部件重量清单.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
   <si>
     <t xml:space="preserve">部件</t>
   </si>
@@ -133,6 +133,9 @@
     <t xml:space="preserve">普通螺丝刀</t>
   </si>
   <si>
+    <t xml:space="preserve">镊子</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.0x150mm超长一字螺丝刀</t>
   </si>
   <si>
@@ -155,6 +158,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.5元/10个</t>
+  </si>
+  <si>
+    <t xml:space="preserve">共 4690.66 元</t>
   </si>
 </sst>
 </file>
@@ -237,7 +243,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -272,6 +278,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -291,8 +301,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultColWidth="8.6015625" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D35"/>
+  <sheetFormatPr defaultColWidth="8.59375" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="28.33"/>
@@ -603,31 +613,44 @@
         <v>37</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="2" t="s">
+    </row>
+    <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8" t="s">
+      <c r="B32" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="2" t="s">
+    </row>
+    <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="8" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7" t="s">
+      <c r="B33" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="2" t="s">
+    </row>
+    <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="s">
         <v>44</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
